--- a/output/stock_quant_scores/MSFT_balance_df.xlsx
+++ b/output/stock_quant_scores/MSFT_balance_df.xlsx
@@ -1775,22 +1775,32 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>61270000000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>74602000000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>166542000000</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>84281000000</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>198298000000</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1800,7 +1810,9 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>95082000000</v>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
@@ -1814,7 +1826,9 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>364840000000</v>
+      </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
@@ -1834,10 +1848,14 @@
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>169684000000</v>
+      </c>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>3742000000</v>
+      </c>
       <c r="BP6" t="n">
         <v>1367000000</v>
       </c>
@@ -1853,7 +1871,9 @@
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
+      <c r="BY6" t="n">
+        <v>13931000000</v>
+      </c>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
     </row>
